--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Escritorio\Python +POO\Clases Y objetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18FB720-98DE-43AF-AD78-7368F632E2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9479AF05-BB53-4E22-91E5-A167EEF5237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="216" yWindow="24" windowWidth="22824" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANIMAL" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,28 @@
     <sheet name="FINCAS" sheetId="6" r:id="rId6"/>
     <sheet name="RAZAS" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PARTOS!$A$1:$E$423</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5655" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="622">
   <si>
     <t>ID</t>
   </si>
@@ -1601,6 +1617,297 @@
   </si>
   <si>
     <t>velasquez</t>
+  </si>
+  <si>
+    <t>solo ha parido una vez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 12 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 15 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 0 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 10 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 28 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 28 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 5 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 13 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 26 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 22 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 6 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 22 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 6 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 2 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 24 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 7 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 19 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 7 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Meses 9 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 9 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 1 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Meses 23 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Meses 18 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Meses 1 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 21 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 12 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 25 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 2 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Meses 24 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 11 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 0 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 13 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 27 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 18 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 23 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 26 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 24 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 13 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 8 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 21 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 1 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Meses 8 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 3 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 12 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 29 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Meses 10 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 8 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Meses 29 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 7 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 19 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 2 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 29 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 13 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 3 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Meses 4 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Meses 25 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 1 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 11 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 Meses 18 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Meses 26 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 29 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 12 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 3 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Meses 15 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Meses 4 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 27 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Meses 24 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 22 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 16 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Meses 24 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Meses 6 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 Meses 29 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 17 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Meses 4 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Meses 30 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Meses 14 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Meses 17 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Meses 6 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Meses 1 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Meses 30 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Meses 11 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Meses 23 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Meses 18 Días En Parir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Meses 1 Días En Parir </t>
   </si>
 </sst>
 </file>
@@ -1608,13 +1915,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1640,10 +1953,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2658,6 +2974,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E423"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2686,6 +3007,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E2" t="s">
         <v>62</v>
       </c>
@@ -2700,6 +3024,9 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E3" t="s">
         <v>62</v>
       </c>
@@ -2714,6 +3041,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E4" t="s">
         <v>62</v>
       </c>
@@ -2728,6 +3058,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E5" t="s">
         <v>62</v>
       </c>
@@ -2742,6 +3075,9 @@
       <c r="C6">
         <v>1</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E6" t="s">
         <v>62</v>
       </c>
@@ -2756,6 +3092,9 @@
       <c r="C7">
         <v>1</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
@@ -2770,6 +3109,9 @@
       <c r="C8">
         <v>1</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E8" t="s">
         <v>62</v>
       </c>
@@ -2784,6 +3126,9 @@
       <c r="C9">
         <v>1</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E9" t="s">
         <v>62</v>
       </c>
@@ -2798,6 +3143,9 @@
       <c r="C10">
         <v>1</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E10" t="s">
         <v>62</v>
       </c>
@@ -2812,6 +3160,9 @@
       <c r="C11">
         <v>1</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E11" t="s">
         <v>62</v>
       </c>
@@ -2826,6 +3177,9 @@
       <c r="C12">
         <v>1</v>
       </c>
+      <c r="D12" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E12" t="s">
         <v>62</v>
       </c>
@@ -2840,6 +3194,9 @@
       <c r="C13">
         <v>1</v>
       </c>
+      <c r="D13" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E13" t="s">
         <v>62</v>
       </c>
@@ -2854,6 +3211,9 @@
       <c r="C14">
         <v>1</v>
       </c>
+      <c r="D14" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E14" t="s">
         <v>62</v>
       </c>
@@ -2868,6 +3228,9 @@
       <c r="C15">
         <v>1</v>
       </c>
+      <c r="D15" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E15" t="s">
         <v>62</v>
       </c>
@@ -2882,6 +3245,9 @@
       <c r="C16">
         <v>1</v>
       </c>
+      <c r="D16" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E16" t="s">
         <v>62</v>
       </c>
@@ -2896,6 +3262,9 @@
       <c r="C17">
         <v>1</v>
       </c>
+      <c r="D17" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E17" t="s">
         <v>62</v>
       </c>
@@ -2910,6 +3279,9 @@
       <c r="C18">
         <v>1</v>
       </c>
+      <c r="D18" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E18" t="s">
         <v>62</v>
       </c>
@@ -2924,6 +3296,9 @@
       <c r="C19">
         <v>1</v>
       </c>
+      <c r="D19" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E19" t="s">
         <v>62</v>
       </c>
@@ -2938,6 +3313,9 @@
       <c r="C20">
         <v>1</v>
       </c>
+      <c r="D20" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E20" t="s">
         <v>62</v>
       </c>
@@ -2952,6 +3330,9 @@
       <c r="C21">
         <v>1</v>
       </c>
+      <c r="D21" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E21" t="s">
         <v>62</v>
       </c>
@@ -2966,6 +3347,9 @@
       <c r="C22">
         <v>1</v>
       </c>
+      <c r="D22" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E22" t="s">
         <v>62</v>
       </c>
@@ -2980,6 +3364,9 @@
       <c r="C23">
         <v>1</v>
       </c>
+      <c r="D23" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E23" t="s">
         <v>62</v>
       </c>
@@ -2994,6 +3381,9 @@
       <c r="C24">
         <v>1</v>
       </c>
+      <c r="D24" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
@@ -3008,6 +3398,9 @@
       <c r="C25">
         <v>1</v>
       </c>
+      <c r="D25" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E25" t="s">
         <v>62</v>
       </c>
@@ -3022,6 +3415,9 @@
       <c r="C26">
         <v>1</v>
       </c>
+      <c r="D26" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E26" t="s">
         <v>62</v>
       </c>
@@ -3036,6 +3432,9 @@
       <c r="C27">
         <v>1</v>
       </c>
+      <c r="D27" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E27" t="s">
         <v>62</v>
       </c>
@@ -3050,6 +3449,9 @@
       <c r="C28">
         <v>1</v>
       </c>
+      <c r="D28" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E28" t="s">
         <v>62</v>
       </c>
@@ -3064,6 +3466,9 @@
       <c r="C29">
         <v>1</v>
       </c>
+      <c r="D29" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E29" t="s">
         <v>62</v>
       </c>
@@ -3078,6 +3483,9 @@
       <c r="C30">
         <v>1</v>
       </c>
+      <c r="D30" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E30" t="s">
         <v>62</v>
       </c>
@@ -3092,6 +3500,9 @@
       <c r="C31">
         <v>1</v>
       </c>
+      <c r="D31" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E31" t="s">
         <v>62</v>
       </c>
@@ -3106,6 +3517,9 @@
       <c r="C32">
         <v>1</v>
       </c>
+      <c r="D32" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E32" t="s">
         <v>62</v>
       </c>
@@ -3120,6 +3534,9 @@
       <c r="C33">
         <v>1</v>
       </c>
+      <c r="D33" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E33" t="s">
         <v>62</v>
       </c>
@@ -3134,6 +3551,9 @@
       <c r="C34">
         <v>1</v>
       </c>
+      <c r="D34" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E34" t="s">
         <v>62</v>
       </c>
@@ -3148,6 +3568,9 @@
       <c r="C35">
         <v>1</v>
       </c>
+      <c r="D35" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E35" t="s">
         <v>62</v>
       </c>
@@ -3162,6 +3585,9 @@
       <c r="C36">
         <v>1</v>
       </c>
+      <c r="D36" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E36" t="s">
         <v>62</v>
       </c>
@@ -3176,6 +3602,9 @@
       <c r="C37">
         <v>1</v>
       </c>
+      <c r="D37" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E37" t="s">
         <v>62</v>
       </c>
@@ -3190,6 +3619,9 @@
       <c r="C38">
         <v>1</v>
       </c>
+      <c r="D38" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E38" t="s">
         <v>62</v>
       </c>
@@ -3204,6 +3636,9 @@
       <c r="C39">
         <v>1</v>
       </c>
+      <c r="D39" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E39" t="s">
         <v>62</v>
       </c>
@@ -3218,6 +3653,9 @@
       <c r="C40">
         <v>1</v>
       </c>
+      <c r="D40" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E40" t="s">
         <v>62</v>
       </c>
@@ -3232,6 +3670,9 @@
       <c r="C41">
         <v>1</v>
       </c>
+      <c r="D41" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E41" t="s">
         <v>62</v>
       </c>
@@ -3246,6 +3687,9 @@
       <c r="C42">
         <v>1</v>
       </c>
+      <c r="D42" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E42" t="s">
         <v>62</v>
       </c>
@@ -3260,6 +3704,9 @@
       <c r="C43">
         <v>1</v>
       </c>
+      <c r="D43" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E43" t="s">
         <v>62</v>
       </c>
@@ -3274,6 +3721,9 @@
       <c r="C44">
         <v>1</v>
       </c>
+      <c r="D44" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
@@ -3288,6 +3738,9 @@
       <c r="C45">
         <v>1</v>
       </c>
+      <c r="D45" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E45" t="s">
         <v>62</v>
       </c>
@@ -3302,6 +3755,9 @@
       <c r="C46">
         <v>1</v>
       </c>
+      <c r="D46" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E46" t="s">
         <v>62</v>
       </c>
@@ -3316,6 +3772,9 @@
       <c r="C47">
         <v>1</v>
       </c>
+      <c r="D47" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E47" t="s">
         <v>62</v>
       </c>
@@ -3330,6 +3789,9 @@
       <c r="C48">
         <v>1</v>
       </c>
+      <c r="D48" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E48" t="s">
         <v>62</v>
       </c>
@@ -3344,6 +3806,9 @@
       <c r="C49">
         <v>1</v>
       </c>
+      <c r="D49" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E49" t="s">
         <v>62</v>
       </c>
@@ -3358,6 +3823,9 @@
       <c r="C50">
         <v>1</v>
       </c>
+      <c r="D50" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E50" t="s">
         <v>62</v>
       </c>
@@ -3372,6 +3840,9 @@
       <c r="C51">
         <v>1</v>
       </c>
+      <c r="D51" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E51" t="s">
         <v>62</v>
       </c>
@@ -3386,6 +3857,9 @@
       <c r="C52">
         <v>1</v>
       </c>
+      <c r="D52" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E52" t="s">
         <v>62</v>
       </c>
@@ -3400,6 +3874,9 @@
       <c r="C53">
         <v>1</v>
       </c>
+      <c r="D53" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E53" t="s">
         <v>62</v>
       </c>
@@ -3414,6 +3891,9 @@
       <c r="C54">
         <v>1</v>
       </c>
+      <c r="D54" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E54" t="s">
         <v>62</v>
       </c>
@@ -3428,6 +3908,9 @@
       <c r="C55">
         <v>1</v>
       </c>
+      <c r="D55" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E55" t="s">
         <v>62</v>
       </c>
@@ -3442,6 +3925,9 @@
       <c r="C56">
         <v>1</v>
       </c>
+      <c r="D56" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E56" t="s">
         <v>62</v>
       </c>
@@ -3456,6 +3942,9 @@
       <c r="C57">
         <v>1</v>
       </c>
+      <c r="D57" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E57" t="s">
         <v>62</v>
       </c>
@@ -3470,6 +3959,9 @@
       <c r="C58">
         <v>1</v>
       </c>
+      <c r="D58" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E58" t="s">
         <v>62</v>
       </c>
@@ -3484,6 +3976,9 @@
       <c r="C59">
         <v>1</v>
       </c>
+      <c r="D59" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E59" t="s">
         <v>62</v>
       </c>
@@ -3498,6 +3993,9 @@
       <c r="C60">
         <v>1</v>
       </c>
+      <c r="D60" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E60" t="s">
         <v>62</v>
       </c>
@@ -3512,6 +4010,9 @@
       <c r="C61">
         <v>1</v>
       </c>
+      <c r="D61" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E61" t="s">
         <v>62</v>
       </c>
@@ -3526,6 +4027,9 @@
       <c r="C62">
         <v>1</v>
       </c>
+      <c r="D62" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E62" t="s">
         <v>62</v>
       </c>
@@ -3540,6 +4044,9 @@
       <c r="C63">
         <v>1</v>
       </c>
+      <c r="D63" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E63" t="s">
         <v>62</v>
       </c>
@@ -3554,6 +4061,9 @@
       <c r="C64">
         <v>1</v>
       </c>
+      <c r="D64" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E64" t="s">
         <v>62</v>
       </c>
@@ -3568,6 +4078,9 @@
       <c r="C65">
         <v>1</v>
       </c>
+      <c r="D65" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E65" t="s">
         <v>62</v>
       </c>
@@ -3582,6 +4095,9 @@
       <c r="C66">
         <v>1</v>
       </c>
+      <c r="D66" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E66" t="s">
         <v>62</v>
       </c>
@@ -3596,6 +4112,9 @@
       <c r="C67">
         <v>1</v>
       </c>
+      <c r="D67" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E67" t="s">
         <v>62</v>
       </c>
@@ -3610,6 +4129,9 @@
       <c r="C68">
         <v>1</v>
       </c>
+      <c r="D68" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E68" t="s">
         <v>123</v>
       </c>
@@ -3624,6 +4146,9 @@
       <c r="C69">
         <v>1</v>
       </c>
+      <c r="D69" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E69" t="s">
         <v>123</v>
       </c>
@@ -3638,6 +4163,9 @@
       <c r="C70">
         <v>1</v>
       </c>
+      <c r="D70" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E70" t="s">
         <v>123</v>
       </c>
@@ -3652,6 +4180,9 @@
       <c r="C71">
         <v>1</v>
       </c>
+      <c r="D71" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
@@ -3666,6 +4197,9 @@
       <c r="C72">
         <v>1</v>
       </c>
+      <c r="D72" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E72" t="s">
         <v>62</v>
       </c>
@@ -3680,6 +4214,9 @@
       <c r="C73">
         <v>1</v>
       </c>
+      <c r="D73" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E73" t="s">
         <v>62</v>
       </c>
@@ -3694,6 +4231,9 @@
       <c r="C74">
         <v>1</v>
       </c>
+      <c r="D74" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E74" t="s">
         <v>62</v>
       </c>
@@ -3708,6 +4248,9 @@
       <c r="C75">
         <v>1</v>
       </c>
+      <c r="D75" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E75" t="s">
         <v>62</v>
       </c>
@@ -3722,6 +4265,9 @@
       <c r="C76">
         <v>1</v>
       </c>
+      <c r="D76" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E76" t="s">
         <v>62</v>
       </c>
@@ -3736,6 +4282,9 @@
       <c r="C77">
         <v>1</v>
       </c>
+      <c r="D77" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E77" t="s">
         <v>62</v>
       </c>
@@ -3750,6 +4299,9 @@
       <c r="C78">
         <v>1</v>
       </c>
+      <c r="D78" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E78" t="s">
         <v>62</v>
       </c>
@@ -3764,6 +4316,9 @@
       <c r="C79">
         <v>1</v>
       </c>
+      <c r="D79" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E79" t="s">
         <v>62</v>
       </c>
@@ -3778,6 +4333,9 @@
       <c r="C80">
         <v>1</v>
       </c>
+      <c r="D80" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E80" t="s">
         <v>62</v>
       </c>
@@ -3792,6 +4350,9 @@
       <c r="C81">
         <v>1</v>
       </c>
+      <c r="D81" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E81" t="s">
         <v>62</v>
       </c>
@@ -3806,6 +4367,9 @@
       <c r="C82">
         <v>1</v>
       </c>
+      <c r="D82" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E82" t="s">
         <v>62</v>
       </c>
@@ -3820,6 +4384,9 @@
       <c r="C83">
         <v>1</v>
       </c>
+      <c r="D83" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E83" t="s">
         <v>62</v>
       </c>
@@ -3834,6 +4401,9 @@
       <c r="C84">
         <v>1</v>
       </c>
+      <c r="D84" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E84" t="s">
         <v>62</v>
       </c>
@@ -3848,6 +4418,9 @@
       <c r="C85">
         <v>1</v>
       </c>
+      <c r="D85" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E85" t="s">
         <v>62</v>
       </c>
@@ -3862,6 +4435,9 @@
       <c r="C86">
         <v>1</v>
       </c>
+      <c r="D86" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E86" t="s">
         <v>62</v>
       </c>
@@ -3876,6 +4452,9 @@
       <c r="C87">
         <v>1</v>
       </c>
+      <c r="D87" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E87" t="s">
         <v>62</v>
       </c>
@@ -3890,6 +4469,9 @@
       <c r="C88">
         <v>1</v>
       </c>
+      <c r="D88" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E88" t="s">
         <v>62</v>
       </c>
@@ -3904,6 +4486,9 @@
       <c r="C89">
         <v>1</v>
       </c>
+      <c r="D89" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E89" t="s">
         <v>62</v>
       </c>
@@ -3918,6 +4503,9 @@
       <c r="C90">
         <v>1</v>
       </c>
+      <c r="D90" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E90" t="s">
         <v>62</v>
       </c>
@@ -3932,6 +4520,9 @@
       <c r="C91">
         <v>1</v>
       </c>
+      <c r="D91" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E91" t="s">
         <v>62</v>
       </c>
@@ -3946,6 +4537,9 @@
       <c r="C92">
         <v>1</v>
       </c>
+      <c r="D92" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E92" t="s">
         <v>62</v>
       </c>
@@ -3960,6 +4554,9 @@
       <c r="C93">
         <v>1</v>
       </c>
+      <c r="D93" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E93" t="s">
         <v>62</v>
       </c>
@@ -3974,6 +4571,9 @@
       <c r="C94">
         <v>1</v>
       </c>
+      <c r="D94" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E94" t="s">
         <v>62</v>
       </c>
@@ -3988,6 +4588,9 @@
       <c r="C95">
         <v>1</v>
       </c>
+      <c r="D95" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E95" t="s">
         <v>62</v>
       </c>
@@ -4002,6 +4605,9 @@
       <c r="C96">
         <v>1</v>
       </c>
+      <c r="D96" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E96" t="s">
         <v>62</v>
       </c>
@@ -4016,6 +4622,9 @@
       <c r="C97">
         <v>1</v>
       </c>
+      <c r="D97" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E97" t="s">
         <v>62</v>
       </c>
@@ -4030,6 +4639,9 @@
       <c r="C98">
         <v>2</v>
       </c>
+      <c r="D98" t="s">
+        <v>526</v>
+      </c>
       <c r="E98" t="s">
         <v>62</v>
       </c>
@@ -4044,6 +4656,9 @@
       <c r="C99">
         <v>1</v>
       </c>
+      <c r="D99" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E99" t="s">
         <v>62</v>
       </c>
@@ -4058,6 +4673,9 @@
       <c r="C100">
         <v>1</v>
       </c>
+      <c r="D100" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E100" t="s">
         <v>62</v>
       </c>
@@ -4072,6 +4690,9 @@
       <c r="C101">
         <v>1</v>
       </c>
+      <c r="D101" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E101" t="s">
         <v>62</v>
       </c>
@@ -4086,6 +4707,9 @@
       <c r="C102">
         <v>1</v>
       </c>
+      <c r="D102" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E102" t="s">
         <v>62</v>
       </c>
@@ -4100,6 +4724,9 @@
       <c r="C103">
         <v>1</v>
       </c>
+      <c r="D103" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E103" t="s">
         <v>62</v>
       </c>
@@ -4114,6 +4741,9 @@
       <c r="C104">
         <v>1</v>
       </c>
+      <c r="D104" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E104" t="s">
         <v>62</v>
       </c>
@@ -4128,6 +4758,9 @@
       <c r="C105">
         <v>1</v>
       </c>
+      <c r="D105" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E105" t="s">
         <v>62</v>
       </c>
@@ -4142,6 +4775,9 @@
       <c r="C106">
         <v>1</v>
       </c>
+      <c r="D106" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E106" t="s">
         <v>62</v>
       </c>
@@ -4156,6 +4792,9 @@
       <c r="C107">
         <v>1</v>
       </c>
+      <c r="D107" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E107" t="s">
         <v>62</v>
       </c>
@@ -4170,6 +4809,9 @@
       <c r="C108">
         <v>1</v>
       </c>
+      <c r="D108" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E108" t="s">
         <v>62</v>
       </c>
@@ -4184,6 +4826,9 @@
       <c r="C109">
         <v>1</v>
       </c>
+      <c r="D109" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E109" t="s">
         <v>62</v>
       </c>
@@ -4198,6 +4843,9 @@
       <c r="C110">
         <v>1</v>
       </c>
+      <c r="D110" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E110" t="s">
         <v>62</v>
       </c>
@@ -4212,6 +4860,9 @@
       <c r="C111">
         <v>1</v>
       </c>
+      <c r="D111" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E111" t="s">
         <v>62</v>
       </c>
@@ -4226,6 +4877,9 @@
       <c r="C112">
         <v>1</v>
       </c>
+      <c r="D112" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E112" t="s">
         <v>62</v>
       </c>
@@ -4240,6 +4894,9 @@
       <c r="C113">
         <v>1</v>
       </c>
+      <c r="D113" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E113" t="s">
         <v>62</v>
       </c>
@@ -4254,6 +4911,9 @@
       <c r="C114">
         <v>1</v>
       </c>
+      <c r="D114" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E114" t="s">
         <v>62</v>
       </c>
@@ -4268,6 +4928,9 @@
       <c r="C115">
         <v>1</v>
       </c>
+      <c r="D115" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E115" t="s">
         <v>62</v>
       </c>
@@ -4282,6 +4945,9 @@
       <c r="C116">
         <v>1</v>
       </c>
+      <c r="D116" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E116" t="s">
         <v>62</v>
       </c>
@@ -4296,6 +4962,9 @@
       <c r="C117">
         <v>1</v>
       </c>
+      <c r="D117" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E117" t="s">
         <v>62</v>
       </c>
@@ -4310,6 +4979,9 @@
       <c r="C118">
         <v>1</v>
       </c>
+      <c r="D118" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E118" t="s">
         <v>62</v>
       </c>
@@ -4324,6 +4996,9 @@
       <c r="C119">
         <v>1</v>
       </c>
+      <c r="D119" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E119" t="s">
         <v>62</v>
       </c>
@@ -4338,6 +5013,9 @@
       <c r="C120">
         <v>1</v>
       </c>
+      <c r="D120" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E120" t="s">
         <v>62</v>
       </c>
@@ -4352,6 +5030,9 @@
       <c r="C121">
         <v>1</v>
       </c>
+      <c r="D121" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E121" t="s">
         <v>62</v>
       </c>
@@ -4366,6 +5047,9 @@
       <c r="C122">
         <v>1</v>
       </c>
+      <c r="D122" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E122" t="s">
         <v>62</v>
       </c>
@@ -4380,6 +5064,9 @@
       <c r="C123">
         <v>1</v>
       </c>
+      <c r="D123" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E123" t="s">
         <v>62</v>
       </c>
@@ -4394,6 +5081,9 @@
       <c r="C124">
         <v>1</v>
       </c>
+      <c r="D124" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E124" t="s">
         <v>62</v>
       </c>
@@ -4408,6 +5098,9 @@
       <c r="C125">
         <v>1</v>
       </c>
+      <c r="D125" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E125" t="s">
         <v>62</v>
       </c>
@@ -4422,6 +5115,9 @@
       <c r="C126">
         <v>1</v>
       </c>
+      <c r="D126" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E126" t="s">
         <v>62</v>
       </c>
@@ -4436,6 +5132,9 @@
       <c r="C127">
         <v>1</v>
       </c>
+      <c r="D127" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E127" t="s">
         <v>62</v>
       </c>
@@ -4450,6 +5149,9 @@
       <c r="C128">
         <v>1</v>
       </c>
+      <c r="D128" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E128" t="s">
         <v>62</v>
       </c>
@@ -4464,6 +5166,9 @@
       <c r="C129">
         <v>1</v>
       </c>
+      <c r="D129" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E129" t="s">
         <v>62</v>
       </c>
@@ -4478,6 +5183,9 @@
       <c r="C130">
         <v>1</v>
       </c>
+      <c r="D130" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E130" t="s">
         <v>62</v>
       </c>
@@ -4492,6 +5200,9 @@
       <c r="C131">
         <v>1</v>
       </c>
+      <c r="D131" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E131" t="s">
         <v>62</v>
       </c>
@@ -4506,6 +5217,9 @@
       <c r="C132">
         <v>1</v>
       </c>
+      <c r="D132" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E132" t="s">
         <v>62</v>
       </c>
@@ -4520,6 +5234,9 @@
       <c r="C133">
         <v>1</v>
       </c>
+      <c r="D133" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E133" t="s">
         <v>62</v>
       </c>
@@ -4534,6 +5251,9 @@
       <c r="C134">
         <v>1</v>
       </c>
+      <c r="D134" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E134" t="s">
         <v>62</v>
       </c>
@@ -4548,6 +5268,9 @@
       <c r="C135">
         <v>1</v>
       </c>
+      <c r="D135" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E135" t="s">
         <v>62</v>
       </c>
@@ -4562,6 +5285,9 @@
       <c r="C136">
         <v>1</v>
       </c>
+      <c r="D136" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E136" t="s">
         <v>62</v>
       </c>
@@ -4576,6 +5302,9 @@
       <c r="C137">
         <v>1</v>
       </c>
+      <c r="D137" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E137" t="s">
         <v>62</v>
       </c>
@@ -4590,6 +5319,9 @@
       <c r="C138">
         <v>1</v>
       </c>
+      <c r="D138" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E138" t="s">
         <v>62</v>
       </c>
@@ -4604,6 +5336,9 @@
       <c r="C139">
         <v>1</v>
       </c>
+      <c r="D139" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E139" t="s">
         <v>62</v>
       </c>
@@ -4618,6 +5353,9 @@
       <c r="C140">
         <v>1</v>
       </c>
+      <c r="D140" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E140" t="s">
         <v>62</v>
       </c>
@@ -4632,6 +5370,9 @@
       <c r="C141">
         <v>1</v>
       </c>
+      <c r="D141" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E141" t="s">
         <v>62</v>
       </c>
@@ -4646,6 +5387,9 @@
       <c r="C142">
         <v>1</v>
       </c>
+      <c r="D142" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E142" t="s">
         <v>62</v>
       </c>
@@ -4660,6 +5404,9 @@
       <c r="C143">
         <v>1</v>
       </c>
+      <c r="D143" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E143" t="s">
         <v>62</v>
       </c>
@@ -4674,6 +5421,9 @@
       <c r="C144">
         <v>1</v>
       </c>
+      <c r="D144" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E144" t="s">
         <v>62</v>
       </c>
@@ -4688,6 +5438,9 @@
       <c r="C145">
         <v>1</v>
       </c>
+      <c r="D145" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E145" t="s">
         <v>62</v>
       </c>
@@ -4702,6 +5455,9 @@
       <c r="C146">
         <v>1</v>
       </c>
+      <c r="D146" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E146" t="s">
         <v>62</v>
       </c>
@@ -4716,6 +5472,9 @@
       <c r="C147">
         <v>1</v>
       </c>
+      <c r="D147" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E147" t="s">
         <v>62</v>
       </c>
@@ -4730,6 +5489,9 @@
       <c r="C148">
         <v>1</v>
       </c>
+      <c r="D148" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E148" t="s">
         <v>62</v>
       </c>
@@ -4744,6 +5506,9 @@
       <c r="C149">
         <v>1</v>
       </c>
+      <c r="D149" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E149" t="s">
         <v>62</v>
       </c>
@@ -4758,6 +5523,9 @@
       <c r="C150">
         <v>1</v>
       </c>
+      <c r="D150" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E150" t="s">
         <v>62</v>
       </c>
@@ -4772,6 +5540,9 @@
       <c r="C151">
         <v>1</v>
       </c>
+      <c r="D151" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E151" t="s">
         <v>62</v>
       </c>
@@ -4786,6 +5557,9 @@
       <c r="C152">
         <v>1</v>
       </c>
+      <c r="D152" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E152" t="s">
         <v>62</v>
       </c>
@@ -4800,6 +5574,9 @@
       <c r="C153">
         <v>1</v>
       </c>
+      <c r="D153" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E153" t="s">
         <v>62</v>
       </c>
@@ -4814,6 +5591,9 @@
       <c r="C154">
         <v>1</v>
       </c>
+      <c r="D154" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E154" t="s">
         <v>62</v>
       </c>
@@ -4828,6 +5608,9 @@
       <c r="C155">
         <v>1</v>
       </c>
+      <c r="D155" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E155" t="s">
         <v>62</v>
       </c>
@@ -4842,6 +5625,9 @@
       <c r="C156">
         <v>1</v>
       </c>
+      <c r="D156" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E156" t="s">
         <v>62</v>
       </c>
@@ -4856,6 +5642,9 @@
       <c r="C157">
         <v>1</v>
       </c>
+      <c r="D157" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E157" t="s">
         <v>62</v>
       </c>
@@ -4870,6 +5659,9 @@
       <c r="C158">
         <v>1</v>
       </c>
+      <c r="D158" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E158" t="s">
         <v>62</v>
       </c>
@@ -4884,6 +5676,9 @@
       <c r="C159">
         <v>1</v>
       </c>
+      <c r="D159" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E159" t="s">
         <v>62</v>
       </c>
@@ -4898,6 +5693,9 @@
       <c r="C160">
         <v>1</v>
       </c>
+      <c r="D160" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E160" t="s">
         <v>62</v>
       </c>
@@ -4912,6 +5710,9 @@
       <c r="C161">
         <v>1</v>
       </c>
+      <c r="D161" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E161" t="s">
         <v>62</v>
       </c>
@@ -4926,6 +5727,9 @@
       <c r="C162">
         <v>1</v>
       </c>
+      <c r="D162" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E162" t="s">
         <v>62</v>
       </c>
@@ -4940,6 +5744,9 @@
       <c r="C163">
         <v>1</v>
       </c>
+      <c r="D163" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E163" t="s">
         <v>62</v>
       </c>
@@ -4954,6 +5761,9 @@
       <c r="C164">
         <v>1</v>
       </c>
+      <c r="D164" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E164" t="s">
         <v>62</v>
       </c>
@@ -4968,6 +5778,9 @@
       <c r="C165">
         <v>1</v>
       </c>
+      <c r="D165" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E165" t="s">
         <v>62</v>
       </c>
@@ -4982,6 +5795,9 @@
       <c r="C166">
         <v>1</v>
       </c>
+      <c r="D166" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E166" t="s">
         <v>62</v>
       </c>
@@ -4996,6 +5812,9 @@
       <c r="C167">
         <v>1</v>
       </c>
+      <c r="D167" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E167" t="s">
         <v>62</v>
       </c>
@@ -5010,6 +5829,9 @@
       <c r="C168">
         <v>1</v>
       </c>
+      <c r="D168" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E168" t="s">
         <v>62</v>
       </c>
@@ -5024,6 +5846,9 @@
       <c r="C169">
         <v>1</v>
       </c>
+      <c r="D169" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E169" t="s">
         <v>62</v>
       </c>
@@ -5038,6 +5863,9 @@
       <c r="C170">
         <v>1</v>
       </c>
+      <c r="D170" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E170" t="s">
         <v>62</v>
       </c>
@@ -5052,6 +5880,9 @@
       <c r="C171">
         <v>1</v>
       </c>
+      <c r="D171" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E171" t="s">
         <v>62</v>
       </c>
@@ -5066,6 +5897,9 @@
       <c r="C172">
         <v>1</v>
       </c>
+      <c r="D172" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E172" t="s">
         <v>62</v>
       </c>
@@ -5080,6 +5914,9 @@
       <c r="C173">
         <v>1</v>
       </c>
+      <c r="D173" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E173" t="s">
         <v>62</v>
       </c>
@@ -5094,6 +5931,9 @@
       <c r="C174">
         <v>1</v>
       </c>
+      <c r="D174" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E174" t="s">
         <v>62</v>
       </c>
@@ -5108,6 +5948,9 @@
       <c r="C175">
         <v>1</v>
       </c>
+      <c r="D175" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E175" t="s">
         <v>62</v>
       </c>
@@ -5122,6 +5965,9 @@
       <c r="C176">
         <v>1</v>
       </c>
+      <c r="D176" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E176" t="s">
         <v>62</v>
       </c>
@@ -5136,6 +5982,9 @@
       <c r="C177">
         <v>1</v>
       </c>
+      <c r="D177" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E177" t="s">
         <v>62</v>
       </c>
@@ -5150,6 +5999,9 @@
       <c r="C178">
         <v>1</v>
       </c>
+      <c r="D178" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E178" t="s">
         <v>62</v>
       </c>
@@ -5164,6 +6016,9 @@
       <c r="C179">
         <v>1</v>
       </c>
+      <c r="D179" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E179" t="s">
         <v>62</v>
       </c>
@@ -5178,6 +6033,9 @@
       <c r="C180">
         <v>1</v>
       </c>
+      <c r="D180" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E180" t="s">
         <v>62</v>
       </c>
@@ -5192,6 +6050,9 @@
       <c r="C181">
         <v>1</v>
       </c>
+      <c r="D181" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E181" t="s">
         <v>62</v>
       </c>
@@ -5206,6 +6067,9 @@
       <c r="C182">
         <v>1</v>
       </c>
+      <c r="D182" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E182" t="s">
         <v>62</v>
       </c>
@@ -5220,6 +6084,9 @@
       <c r="C183">
         <v>1</v>
       </c>
+      <c r="D183" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E183" t="s">
         <v>62</v>
       </c>
@@ -5234,6 +6101,9 @@
       <c r="C184">
         <v>1</v>
       </c>
+      <c r="D184" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E184" t="s">
         <v>62</v>
       </c>
@@ -5248,6 +6118,9 @@
       <c r="C185">
         <v>1</v>
       </c>
+      <c r="D185" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E185" t="s">
         <v>62</v>
       </c>
@@ -5262,6 +6135,9 @@
       <c r="C186">
         <v>1</v>
       </c>
+      <c r="D186" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E186" t="s">
         <v>62</v>
       </c>
@@ -5276,6 +6152,9 @@
       <c r="C187">
         <v>1</v>
       </c>
+      <c r="D187" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E187" t="s">
         <v>62</v>
       </c>
@@ -5290,6 +6169,9 @@
       <c r="C188">
         <v>1</v>
       </c>
+      <c r="D188" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E188" t="s">
         <v>62</v>
       </c>
@@ -5304,6 +6186,9 @@
       <c r="C189">
         <v>1</v>
       </c>
+      <c r="D189" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E189" t="s">
         <v>62</v>
       </c>
@@ -5318,6 +6203,9 @@
       <c r="C190">
         <v>1</v>
       </c>
+      <c r="D190" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E190" t="s">
         <v>62</v>
       </c>
@@ -5332,6 +6220,9 @@
       <c r="C191">
         <v>1</v>
       </c>
+      <c r="D191" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E191" t="s">
         <v>62</v>
       </c>
@@ -5346,6 +6237,9 @@
       <c r="C192">
         <v>1</v>
       </c>
+      <c r="D192" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E192" t="s">
         <v>62</v>
       </c>
@@ -5360,6 +6254,9 @@
       <c r="C193">
         <v>1</v>
       </c>
+      <c r="D193" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E193" t="s">
         <v>62</v>
       </c>
@@ -5374,6 +6271,9 @@
       <c r="C194">
         <v>1</v>
       </c>
+      <c r="D194" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E194" t="s">
         <v>62</v>
       </c>
@@ -5388,6 +6288,9 @@
       <c r="C195">
         <v>1</v>
       </c>
+      <c r="D195" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E195" t="s">
         <v>62</v>
       </c>
@@ -5402,6 +6305,9 @@
       <c r="C196">
         <v>1</v>
       </c>
+      <c r="D196" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E196" t="s">
         <v>62</v>
       </c>
@@ -5416,6 +6322,9 @@
       <c r="C197">
         <v>1</v>
       </c>
+      <c r="D197" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E197" t="s">
         <v>62</v>
       </c>
@@ -5430,6 +6339,9 @@
       <c r="C198">
         <v>2</v>
       </c>
+      <c r="D198" t="s">
+        <v>527</v>
+      </c>
       <c r="E198" t="s">
         <v>62</v>
       </c>
@@ -5444,6 +6356,9 @@
       <c r="C199">
         <v>1</v>
       </c>
+      <c r="D199" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E199" t="s">
         <v>62</v>
       </c>
@@ -5458,6 +6373,9 @@
       <c r="C200">
         <v>1</v>
       </c>
+      <c r="D200" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E200" t="s">
         <v>62</v>
       </c>
@@ -5472,6 +6390,9 @@
       <c r="C201">
         <v>1</v>
       </c>
+      <c r="D201" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E201" t="s">
         <v>62</v>
       </c>
@@ -5486,6 +6407,9 @@
       <c r="C202">
         <v>1</v>
       </c>
+      <c r="D202" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E202" t="s">
         <v>62</v>
       </c>
@@ -5500,6 +6424,9 @@
       <c r="C203">
         <v>1</v>
       </c>
+      <c r="D203" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E203" t="s">
         <v>62</v>
       </c>
@@ -5514,6 +6441,9 @@
       <c r="C204">
         <v>1</v>
       </c>
+      <c r="D204" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E204" t="s">
         <v>62</v>
       </c>
@@ -5528,6 +6458,9 @@
       <c r="C205">
         <v>1</v>
       </c>
+      <c r="D205" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E205" t="s">
         <v>62</v>
       </c>
@@ -5542,6 +6475,9 @@
       <c r="C206">
         <v>1</v>
       </c>
+      <c r="D206" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E206" t="s">
         <v>62</v>
       </c>
@@ -5556,6 +6492,9 @@
       <c r="C207">
         <v>1</v>
       </c>
+      <c r="D207" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E207" t="s">
         <v>62</v>
       </c>
@@ -5570,6 +6509,9 @@
       <c r="C208">
         <v>1</v>
       </c>
+      <c r="D208" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E208" t="s">
         <v>62</v>
       </c>
@@ -5584,6 +6526,9 @@
       <c r="C209">
         <v>1</v>
       </c>
+      <c r="D209" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E209" t="s">
         <v>123</v>
       </c>
@@ -5598,6 +6543,9 @@
       <c r="C210">
         <v>2</v>
       </c>
+      <c r="D210" t="s">
+        <v>528</v>
+      </c>
       <c r="E210" t="s">
         <v>123</v>
       </c>
@@ -5612,6 +6560,9 @@
       <c r="C211">
         <v>1</v>
       </c>
+      <c r="D211" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E211" t="s">
         <v>123</v>
       </c>
@@ -5626,6 +6577,9 @@
       <c r="C212">
         <v>1</v>
       </c>
+      <c r="D212" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E212" t="s">
         <v>62</v>
       </c>
@@ -5640,6 +6594,9 @@
       <c r="C213">
         <v>1</v>
       </c>
+      <c r="D213" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E213" t="s">
         <v>123</v>
       </c>
@@ -5654,6 +6611,9 @@
       <c r="C214">
         <v>1</v>
       </c>
+      <c r="D214" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E214" t="s">
         <v>123</v>
       </c>
@@ -5668,6 +6628,9 @@
       <c r="C215">
         <v>1</v>
       </c>
+      <c r="D215" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E215" t="s">
         <v>123</v>
       </c>
@@ -5682,6 +6645,9 @@
       <c r="C216">
         <v>2</v>
       </c>
+      <c r="D216" t="s">
+        <v>529</v>
+      </c>
       <c r="E216" t="s">
         <v>62</v>
       </c>
@@ -5696,6 +6662,9 @@
       <c r="C217">
         <v>1</v>
       </c>
+      <c r="D217" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E217" t="s">
         <v>62</v>
       </c>
@@ -5710,6 +6679,9 @@
       <c r="C218">
         <v>1</v>
       </c>
+      <c r="D218" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E218" t="s">
         <v>242</v>
       </c>
@@ -5724,6 +6696,9 @@
       <c r="C219">
         <v>1</v>
       </c>
+      <c r="D219" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E219" t="s">
         <v>242</v>
       </c>
@@ -5738,6 +6713,9 @@
       <c r="C220">
         <v>1</v>
       </c>
+      <c r="D220" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E220" t="s">
         <v>62</v>
       </c>
@@ -5752,6 +6730,9 @@
       <c r="C221">
         <v>1</v>
       </c>
+      <c r="D221" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E221" t="s">
         <v>62</v>
       </c>
@@ -5766,6 +6747,9 @@
       <c r="C222">
         <v>1</v>
       </c>
+      <c r="D222" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E222" t="s">
         <v>62</v>
       </c>
@@ -5780,6 +6764,9 @@
       <c r="C223">
         <v>1</v>
       </c>
+      <c r="D223" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E223" t="s">
         <v>62</v>
       </c>
@@ -5794,6 +6781,9 @@
       <c r="C224">
         <v>1</v>
       </c>
+      <c r="D224" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E224" t="s">
         <v>62</v>
       </c>
@@ -5808,6 +6798,9 @@
       <c r="C225">
         <v>1</v>
       </c>
+      <c r="D225" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E225" t="s">
         <v>62</v>
       </c>
@@ -5822,6 +6815,9 @@
       <c r="C226">
         <v>1</v>
       </c>
+      <c r="D226" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E226" t="s">
         <v>62</v>
       </c>
@@ -5836,6 +6832,9 @@
       <c r="C227">
         <v>2</v>
       </c>
+      <c r="D227" t="s">
+        <v>530</v>
+      </c>
       <c r="E227" t="s">
         <v>62</v>
       </c>
@@ -5850,6 +6849,9 @@
       <c r="C228">
         <v>1</v>
       </c>
+      <c r="D228" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E228" t="s">
         <v>62</v>
       </c>
@@ -5864,6 +6866,9 @@
       <c r="C229">
         <v>1</v>
       </c>
+      <c r="D229" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E229" t="s">
         <v>62</v>
       </c>
@@ -5878,6 +6883,9 @@
       <c r="C230">
         <v>1</v>
       </c>
+      <c r="D230" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E230" t="s">
         <v>62</v>
       </c>
@@ -5892,6 +6900,9 @@
       <c r="C231">
         <v>1</v>
       </c>
+      <c r="D231" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E231" t="s">
         <v>62</v>
       </c>
@@ -5906,6 +6917,9 @@
       <c r="C232">
         <v>1</v>
       </c>
+      <c r="D232" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E232" t="s">
         <v>62</v>
       </c>
@@ -5920,6 +6934,9 @@
       <c r="C233">
         <v>2</v>
       </c>
+      <c r="D233" t="s">
+        <v>531</v>
+      </c>
       <c r="E233" t="s">
         <v>62</v>
       </c>
@@ -5934,6 +6951,9 @@
       <c r="C234">
         <v>2</v>
       </c>
+      <c r="D234" t="s">
+        <v>532</v>
+      </c>
       <c r="E234" t="s">
         <v>62</v>
       </c>
@@ -5948,6 +6968,9 @@
       <c r="C235">
         <v>1</v>
       </c>
+      <c r="D235" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E235" t="s">
         <v>62</v>
       </c>
@@ -5962,6 +6985,9 @@
       <c r="C236">
         <v>2</v>
       </c>
+      <c r="D236" t="s">
+        <v>533</v>
+      </c>
       <c r="E236" t="s">
         <v>62</v>
       </c>
@@ -5976,6 +7002,9 @@
       <c r="C237">
         <v>1</v>
       </c>
+      <c r="D237" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E237" t="s">
         <v>62</v>
       </c>
@@ -5990,6 +7019,9 @@
       <c r="C238">
         <v>1</v>
       </c>
+      <c r="D238" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E238" t="s">
         <v>62</v>
       </c>
@@ -6004,6 +7036,9 @@
       <c r="C239">
         <v>2</v>
       </c>
+      <c r="D239" t="s">
+        <v>534</v>
+      </c>
       <c r="E239" t="s">
         <v>62</v>
       </c>
@@ -6018,6 +7053,9 @@
       <c r="C240">
         <v>1</v>
       </c>
+      <c r="D240" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E240" t="s">
         <v>62</v>
       </c>
@@ -6032,6 +7070,9 @@
       <c r="C241">
         <v>1</v>
       </c>
+      <c r="D241" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E241" t="s">
         <v>62</v>
       </c>
@@ -6046,6 +7087,9 @@
       <c r="C242">
         <v>1</v>
       </c>
+      <c r="D242" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E242" t="s">
         <v>62</v>
       </c>
@@ -6060,6 +7104,9 @@
       <c r="C243">
         <v>2</v>
       </c>
+      <c r="D243" t="s">
+        <v>535</v>
+      </c>
       <c r="E243" t="s">
         <v>62</v>
       </c>
@@ -6074,6 +7121,9 @@
       <c r="C244">
         <v>2</v>
       </c>
+      <c r="D244" t="s">
+        <v>535</v>
+      </c>
       <c r="E244" t="s">
         <v>62</v>
       </c>
@@ -6088,6 +7138,9 @@
       <c r="C245">
         <v>2</v>
       </c>
+      <c r="D245" t="s">
+        <v>536</v>
+      </c>
       <c r="E245" t="s">
         <v>62</v>
       </c>
@@ -6102,6 +7155,9 @@
       <c r="C246">
         <v>2</v>
       </c>
+      <c r="D246" t="s">
+        <v>537</v>
+      </c>
       <c r="E246" t="s">
         <v>62</v>
       </c>
@@ -6116,6 +7172,9 @@
       <c r="C247">
         <v>2</v>
       </c>
+      <c r="D247" t="s">
+        <v>530</v>
+      </c>
       <c r="E247" t="s">
         <v>62</v>
       </c>
@@ -6130,6 +7189,9 @@
       <c r="C248">
         <v>1</v>
       </c>
+      <c r="D248" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E248" t="s">
         <v>62</v>
       </c>
@@ -6144,6 +7206,9 @@
       <c r="C249">
         <v>1</v>
       </c>
+      <c r="D249" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E249" t="s">
         <v>62</v>
       </c>
@@ -6158,6 +7223,9 @@
       <c r="C250">
         <v>1</v>
       </c>
+      <c r="D250" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E250" t="s">
         <v>62</v>
       </c>
@@ -6172,6 +7240,9 @@
       <c r="C251">
         <v>1</v>
       </c>
+      <c r="D251" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E251" t="s">
         <v>62</v>
       </c>
@@ -6186,6 +7257,9 @@
       <c r="C252">
         <v>1</v>
       </c>
+      <c r="D252" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E252" t="s">
         <v>62</v>
       </c>
@@ -6200,6 +7274,9 @@
       <c r="C253">
         <v>1</v>
       </c>
+      <c r="D253" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E253" t="s">
         <v>62</v>
       </c>
@@ -6214,6 +7291,9 @@
       <c r="C254">
         <v>1</v>
       </c>
+      <c r="D254" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E254" t="s">
         <v>62</v>
       </c>
@@ -6228,6 +7308,9 @@
       <c r="C255">
         <v>1</v>
       </c>
+      <c r="D255" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E255" t="s">
         <v>62</v>
       </c>
@@ -6242,6 +7325,9 @@
       <c r="C256">
         <v>1</v>
       </c>
+      <c r="D256" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E256" t="s">
         <v>62</v>
       </c>
@@ -6256,6 +7342,9 @@
       <c r="C257">
         <v>1</v>
       </c>
+      <c r="D257" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E257" t="s">
         <v>62</v>
       </c>
@@ -6270,6 +7359,9 @@
       <c r="C258">
         <v>2</v>
       </c>
+      <c r="D258" t="s">
+        <v>538</v>
+      </c>
       <c r="E258" t="s">
         <v>62</v>
       </c>
@@ -6284,6 +7376,9 @@
       <c r="C259">
         <v>1</v>
       </c>
+      <c r="D259" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E259" t="s">
         <v>62</v>
       </c>
@@ -6298,6 +7393,9 @@
       <c r="C260">
         <v>2</v>
       </c>
+      <c r="D260" t="s">
+        <v>539</v>
+      </c>
       <c r="E260" t="s">
         <v>62</v>
       </c>
@@ -6312,6 +7410,9 @@
       <c r="C261">
         <v>1</v>
       </c>
+      <c r="D261" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E261" t="s">
         <v>62</v>
       </c>
@@ -6326,6 +7427,9 @@
       <c r="C262">
         <v>2</v>
       </c>
+      <c r="D262" t="s">
+        <v>540</v>
+      </c>
       <c r="E262" t="s">
         <v>62</v>
       </c>
@@ -6340,6 +7444,9 @@
       <c r="C263">
         <v>1</v>
       </c>
+      <c r="D263" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E263" t="s">
         <v>62</v>
       </c>
@@ -6354,6 +7461,9 @@
       <c r="C264">
         <v>1</v>
       </c>
+      <c r="D264" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E264" t="s">
         <v>62</v>
       </c>
@@ -6368,6 +7478,9 @@
       <c r="C265">
         <v>1</v>
       </c>
+      <c r="D265" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E265" t="s">
         <v>62</v>
       </c>
@@ -6382,6 +7495,9 @@
       <c r="C266">
         <v>1</v>
       </c>
+      <c r="D266" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E266" t="s">
         <v>62</v>
       </c>
@@ -6396,6 +7512,9 @@
       <c r="C267">
         <v>1</v>
       </c>
+      <c r="D267" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E267" t="s">
         <v>62</v>
       </c>
@@ -6410,6 +7529,9 @@
       <c r="C268">
         <v>2</v>
       </c>
+      <c r="D268" t="s">
+        <v>541</v>
+      </c>
       <c r="E268" t="s">
         <v>62</v>
       </c>
@@ -6424,6 +7546,9 @@
       <c r="C269">
         <v>1</v>
       </c>
+      <c r="D269" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E269" t="s">
         <v>279</v>
       </c>
@@ -6438,6 +7563,9 @@
       <c r="C270">
         <v>2</v>
       </c>
+      <c r="D270" t="s">
+        <v>542</v>
+      </c>
       <c r="E270" t="s">
         <v>62</v>
       </c>
@@ -6452,6 +7580,9 @@
       <c r="C271">
         <v>1</v>
       </c>
+      <c r="D271" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E271" t="s">
         <v>62</v>
       </c>
@@ -6466,6 +7597,9 @@
       <c r="C272">
         <v>2</v>
       </c>
+      <c r="D272" t="s">
+        <v>543</v>
+      </c>
       <c r="E272" t="s">
         <v>62</v>
       </c>
@@ -6480,6 +7614,9 @@
       <c r="C273">
         <v>2</v>
       </c>
+      <c r="D273" t="s">
+        <v>544</v>
+      </c>
       <c r="E273" t="s">
         <v>281</v>
       </c>
@@ -6494,6 +7631,9 @@
       <c r="C274">
         <v>2</v>
       </c>
+      <c r="D274" t="s">
+        <v>545</v>
+      </c>
       <c r="E274" t="s">
         <v>62</v>
       </c>
@@ -6508,6 +7648,9 @@
       <c r="C275">
         <v>1</v>
       </c>
+      <c r="D275" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E275" t="s">
         <v>62</v>
       </c>
@@ -6522,6 +7665,9 @@
       <c r="C276">
         <v>2</v>
       </c>
+      <c r="D276" t="s">
+        <v>546</v>
+      </c>
       <c r="E276" t="s">
         <v>62</v>
       </c>
@@ -6536,6 +7682,9 @@
       <c r="C277">
         <v>3</v>
       </c>
+      <c r="D277" t="s">
+        <v>547</v>
+      </c>
       <c r="E277" t="s">
         <v>62</v>
       </c>
@@ -6550,6 +7699,9 @@
       <c r="C278">
         <v>1</v>
       </c>
+      <c r="D278" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E278" t="s">
         <v>62</v>
       </c>
@@ -6564,6 +7716,9 @@
       <c r="C279">
         <v>1</v>
       </c>
+      <c r="D279" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E279" t="s">
         <v>62</v>
       </c>
@@ -6578,6 +7733,9 @@
       <c r="C280">
         <v>2</v>
       </c>
+      <c r="D280" t="s">
+        <v>548</v>
+      </c>
       <c r="E280" t="s">
         <v>62</v>
       </c>
@@ -6592,6 +7750,9 @@
       <c r="C281">
         <v>1</v>
       </c>
+      <c r="D281" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E281" t="s">
         <v>62</v>
       </c>
@@ -6606,6 +7767,9 @@
       <c r="C282">
         <v>2</v>
       </c>
+      <c r="D282" t="s">
+        <v>549</v>
+      </c>
       <c r="E282" t="s">
         <v>62</v>
       </c>
@@ -6620,6 +7784,9 @@
       <c r="C283">
         <v>1</v>
       </c>
+      <c r="D283" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E283" t="s">
         <v>62</v>
       </c>
@@ -6634,6 +7801,9 @@
       <c r="C284">
         <v>1</v>
       </c>
+      <c r="D284" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E284" t="s">
         <v>62</v>
       </c>
@@ -6648,6 +7818,9 @@
       <c r="C285">
         <v>1</v>
       </c>
+      <c r="D285" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E285" t="s">
         <v>62</v>
       </c>
@@ -6662,6 +7835,9 @@
       <c r="C286">
         <v>1</v>
       </c>
+      <c r="D286" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E286" t="s">
         <v>62</v>
       </c>
@@ -6676,6 +7852,9 @@
       <c r="C287">
         <v>1</v>
       </c>
+      <c r="D287" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E287" t="s">
         <v>62</v>
       </c>
@@ -6690,6 +7869,9 @@
       <c r="C288">
         <v>1</v>
       </c>
+      <c r="D288" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E288" t="s">
         <v>292</v>
       </c>
@@ -6704,6 +7886,9 @@
       <c r="C289">
         <v>1</v>
       </c>
+      <c r="D289" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E289" t="s">
         <v>62</v>
       </c>
@@ -6718,6 +7903,9 @@
       <c r="C290">
         <v>2</v>
       </c>
+      <c r="D290" t="s">
+        <v>550</v>
+      </c>
       <c r="E290" t="s">
         <v>62</v>
       </c>
@@ -6732,6 +7920,9 @@
       <c r="C291">
         <v>1</v>
       </c>
+      <c r="D291" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E291" t="s">
         <v>62</v>
       </c>
@@ -6746,6 +7937,9 @@
       <c r="C292">
         <v>1</v>
       </c>
+      <c r="D292" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E292" t="s">
         <v>62</v>
       </c>
@@ -6760,6 +7954,9 @@
       <c r="C293">
         <v>1</v>
       </c>
+      <c r="D293" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E293" t="s">
         <v>62</v>
       </c>
@@ -6774,6 +7971,9 @@
       <c r="C294">
         <v>2</v>
       </c>
+      <c r="D294" t="s">
+        <v>551</v>
+      </c>
       <c r="E294" t="s">
         <v>62</v>
       </c>
@@ -6788,6 +7988,9 @@
       <c r="C295">
         <v>2</v>
       </c>
+      <c r="D295" t="s">
+        <v>552</v>
+      </c>
       <c r="E295" t="s">
         <v>62</v>
       </c>
@@ -6802,6 +8005,9 @@
       <c r="C296">
         <v>1</v>
       </c>
+      <c r="D296" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E296" t="s">
         <v>62</v>
       </c>
@@ -6816,6 +8022,9 @@
       <c r="C297">
         <v>1</v>
       </c>
+      <c r="D297" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E297" t="s">
         <v>62</v>
       </c>
@@ -6830,6 +8039,9 @@
       <c r="C298">
         <v>1</v>
       </c>
+      <c r="D298" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E298" t="s">
         <v>62</v>
       </c>
@@ -6844,6 +8056,9 @@
       <c r="C299">
         <v>1</v>
       </c>
+      <c r="D299" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E299" t="s">
         <v>62</v>
       </c>
@@ -6858,6 +8073,9 @@
       <c r="C300">
         <v>1</v>
       </c>
+      <c r="D300" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E300" t="s">
         <v>62</v>
       </c>
@@ -6872,6 +8090,9 @@
       <c r="C301">
         <v>1</v>
       </c>
+      <c r="D301" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E301" t="s">
         <v>62</v>
       </c>
@@ -6886,6 +8107,9 @@
       <c r="C302">
         <v>1</v>
       </c>
+      <c r="D302" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E302" t="s">
         <v>62</v>
       </c>
@@ -6900,6 +8124,9 @@
       <c r="C303">
         <v>2</v>
       </c>
+      <c r="D303" t="s">
+        <v>553</v>
+      </c>
       <c r="E303" t="s">
         <v>62</v>
       </c>
@@ -6914,6 +8141,9 @@
       <c r="C304">
         <v>1</v>
       </c>
+      <c r="D304" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E304" t="s">
         <v>62</v>
       </c>
@@ -6928,6 +8158,9 @@
       <c r="C305">
         <v>1</v>
       </c>
+      <c r="D305" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E305" t="s">
         <v>62</v>
       </c>
@@ -6942,6 +8175,9 @@
       <c r="C306">
         <v>1</v>
       </c>
+      <c r="D306" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E306" t="s">
         <v>307</v>
       </c>
@@ -6956,6 +8192,9 @@
       <c r="C307">
         <v>1</v>
       </c>
+      <c r="D307" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E307" t="s">
         <v>62</v>
       </c>
@@ -6970,6 +8209,9 @@
       <c r="C308">
         <v>2</v>
       </c>
+      <c r="D308" t="s">
+        <v>554</v>
+      </c>
       <c r="E308" t="s">
         <v>62</v>
       </c>
@@ -6984,6 +8226,9 @@
       <c r="C309">
         <v>2</v>
       </c>
+      <c r="D309" t="s">
+        <v>555</v>
+      </c>
       <c r="E309" t="s">
         <v>62</v>
       </c>
@@ -6998,6 +8243,9 @@
       <c r="C310">
         <v>2</v>
       </c>
+      <c r="D310" t="s">
+        <v>556</v>
+      </c>
       <c r="E310" t="s">
         <v>62</v>
       </c>
@@ -7012,6 +8260,9 @@
       <c r="C311">
         <v>2</v>
       </c>
+      <c r="D311" t="s">
+        <v>557</v>
+      </c>
       <c r="E311" t="s">
         <v>62</v>
       </c>
@@ -7026,6 +8277,9 @@
       <c r="C312">
         <v>1</v>
       </c>
+      <c r="D312" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E312" t="s">
         <v>307</v>
       </c>
@@ -7040,6 +8294,9 @@
       <c r="C313">
         <v>2</v>
       </c>
+      <c r="D313" t="s">
+        <v>558</v>
+      </c>
       <c r="E313" t="s">
         <v>62</v>
       </c>
@@ -7054,6 +8311,9 @@
       <c r="C314">
         <v>1</v>
       </c>
+      <c r="D314" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E314" t="s">
         <v>62</v>
       </c>
@@ -7068,6 +8328,9 @@
       <c r="C315">
         <v>1</v>
       </c>
+      <c r="D315" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E315" t="s">
         <v>62</v>
       </c>
@@ -7082,6 +8345,9 @@
       <c r="C316">
         <v>1</v>
       </c>
+      <c r="D316" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E316" t="s">
         <v>62</v>
       </c>
@@ -7096,6 +8362,9 @@
       <c r="C317">
         <v>1</v>
       </c>
+      <c r="D317" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E317" t="s">
         <v>62</v>
       </c>
@@ -7110,6 +8379,9 @@
       <c r="C318">
         <v>2</v>
       </c>
+      <c r="D318" t="s">
+        <v>559</v>
+      </c>
       <c r="E318" t="s">
         <v>62</v>
       </c>
@@ -7124,6 +8396,9 @@
       <c r="C319">
         <v>1</v>
       </c>
+      <c r="D319" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E319" t="s">
         <v>62</v>
       </c>
@@ -7138,6 +8413,9 @@
       <c r="C320">
         <v>2</v>
       </c>
+      <c r="D320" t="s">
+        <v>560</v>
+      </c>
       <c r="E320" t="s">
         <v>62</v>
       </c>
@@ -7152,6 +8430,9 @@
       <c r="C321">
         <v>2</v>
       </c>
+      <c r="D321" t="s">
+        <v>561</v>
+      </c>
       <c r="E321" t="s">
         <v>62</v>
       </c>
@@ -7166,6 +8447,9 @@
       <c r="C322">
         <v>1</v>
       </c>
+      <c r="D322" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E322" t="s">
         <v>62</v>
       </c>
@@ -7180,6 +8464,9 @@
       <c r="C323">
         <v>1</v>
       </c>
+      <c r="D323" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E323" t="s">
         <v>317</v>
       </c>
@@ -7194,6 +8481,9 @@
       <c r="C324">
         <v>2</v>
       </c>
+      <c r="D324" t="s">
+        <v>562</v>
+      </c>
       <c r="E324" t="s">
         <v>62</v>
       </c>
@@ -7208,6 +8498,9 @@
       <c r="C325">
         <v>1</v>
       </c>
+      <c r="D325" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E325" t="s">
         <v>62</v>
       </c>
@@ -7222,6 +8515,9 @@
       <c r="C326">
         <v>1</v>
       </c>
+      <c r="D326" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E326" t="s">
         <v>62</v>
       </c>
@@ -7236,6 +8532,9 @@
       <c r="C327">
         <v>2</v>
       </c>
+      <c r="D327" t="s">
+        <v>563</v>
+      </c>
       <c r="E327" t="s">
         <v>62</v>
       </c>
@@ -7250,6 +8549,9 @@
       <c r="C328">
         <v>2</v>
       </c>
+      <c r="D328" t="s">
+        <v>564</v>
+      </c>
       <c r="E328" t="s">
         <v>62</v>
       </c>
@@ -7264,6 +8566,9 @@
       <c r="C329">
         <v>1</v>
       </c>
+      <c r="D329" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E329" t="s">
         <v>62</v>
       </c>
@@ -7278,6 +8583,9 @@
       <c r="C330">
         <v>2</v>
       </c>
+      <c r="D330" t="s">
+        <v>565</v>
+      </c>
       <c r="E330" t="s">
         <v>62</v>
       </c>
@@ -7292,6 +8600,9 @@
       <c r="C331">
         <v>2</v>
       </c>
+      <c r="D331" t="s">
+        <v>566</v>
+      </c>
       <c r="E331" t="s">
         <v>62</v>
       </c>
@@ -7306,6 +8617,9 @@
       <c r="C332">
         <v>2</v>
       </c>
+      <c r="D332" t="s">
+        <v>567</v>
+      </c>
       <c r="E332" t="s">
         <v>62</v>
       </c>
@@ -7320,6 +8634,9 @@
       <c r="C333">
         <v>2</v>
       </c>
+      <c r="D333" t="s">
+        <v>568</v>
+      </c>
       <c r="E333" t="s">
         <v>62</v>
       </c>
@@ -7334,6 +8651,9 @@
       <c r="C334">
         <v>1</v>
       </c>
+      <c r="D334" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E334" t="s">
         <v>62</v>
       </c>
@@ -7348,6 +8668,9 @@
       <c r="C335">
         <v>1</v>
       </c>
+      <c r="D335" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E335" t="s">
         <v>317</v>
       </c>
@@ -7362,6 +8685,9 @@
       <c r="C336">
         <v>1</v>
       </c>
+      <c r="D336" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E336" t="s">
         <v>62</v>
       </c>
@@ -7376,6 +8702,9 @@
       <c r="C337">
         <v>3</v>
       </c>
+      <c r="D337" t="s">
+        <v>569</v>
+      </c>
       <c r="E337" t="s">
         <v>62</v>
       </c>
@@ -7390,6 +8719,9 @@
       <c r="C338">
         <v>1</v>
       </c>
+      <c r="D338" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E338" t="s">
         <v>62</v>
       </c>
@@ -7404,6 +8736,9 @@
       <c r="C339">
         <v>3</v>
       </c>
+      <c r="D339" t="s">
+        <v>529</v>
+      </c>
       <c r="E339" t="s">
         <v>62</v>
       </c>
@@ -7418,6 +8753,9 @@
       <c r="C340">
         <v>2</v>
       </c>
+      <c r="D340" t="s">
+        <v>570</v>
+      </c>
       <c r="E340" t="s">
         <v>62</v>
       </c>
@@ -7432,6 +8770,9 @@
       <c r="C341">
         <v>2</v>
       </c>
+      <c r="D341" t="s">
+        <v>543</v>
+      </c>
       <c r="E341" t="s">
         <v>62</v>
       </c>
@@ -7446,6 +8787,9 @@
       <c r="C342">
         <v>2</v>
       </c>
+      <c r="D342" t="s">
+        <v>571</v>
+      </c>
       <c r="E342" t="s">
         <v>62</v>
       </c>
@@ -7460,6 +8804,9 @@
       <c r="C343">
         <v>2</v>
       </c>
+      <c r="D343" t="s">
+        <v>572</v>
+      </c>
       <c r="E343" t="s">
         <v>62</v>
       </c>
@@ -7474,6 +8821,9 @@
       <c r="C344">
         <v>2</v>
       </c>
+      <c r="D344" t="s">
+        <v>573</v>
+      </c>
       <c r="E344" t="s">
         <v>62</v>
       </c>
@@ -7488,6 +8838,9 @@
       <c r="C345">
         <v>1</v>
       </c>
+      <c r="D345" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E345" t="s">
         <v>325</v>
       </c>
@@ -7502,6 +8855,9 @@
       <c r="C346">
         <v>2</v>
       </c>
+      <c r="D346" t="s">
+        <v>525</v>
+      </c>
       <c r="E346" t="s">
         <v>325</v>
       </c>
@@ -7516,6 +8872,9 @@
       <c r="C347">
         <v>2</v>
       </c>
+      <c r="D347" t="s">
+        <v>536</v>
+      </c>
       <c r="E347" t="s">
         <v>62</v>
       </c>
@@ -7530,6 +8889,9 @@
       <c r="C348">
         <v>2</v>
       </c>
+      <c r="D348" t="s">
+        <v>574</v>
+      </c>
       <c r="E348" t="s">
         <v>62</v>
       </c>
@@ -7544,6 +8906,9 @@
       <c r="C349">
         <v>2</v>
       </c>
+      <c r="D349" t="s">
+        <v>575</v>
+      </c>
       <c r="E349" t="s">
         <v>307</v>
       </c>
@@ -7558,6 +8923,9 @@
       <c r="C350">
         <v>2</v>
       </c>
+      <c r="D350" t="s">
+        <v>576</v>
+      </c>
       <c r="E350" t="s">
         <v>62</v>
       </c>
@@ -7572,6 +8940,9 @@
       <c r="C351">
         <v>1</v>
       </c>
+      <c r="D351" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E351" t="s">
         <v>62</v>
       </c>
@@ -7586,6 +8957,9 @@
       <c r="C352">
         <v>2</v>
       </c>
+      <c r="D352" t="s">
+        <v>577</v>
+      </c>
       <c r="E352" t="s">
         <v>62</v>
       </c>
@@ -7600,6 +8974,9 @@
       <c r="C353">
         <v>1</v>
       </c>
+      <c r="D353" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E353" t="s">
         <v>62</v>
       </c>
@@ -7614,6 +8991,9 @@
       <c r="C354">
         <v>1</v>
       </c>
+      <c r="D354" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E354" t="s">
         <v>62</v>
       </c>
@@ -7628,6 +9008,9 @@
       <c r="C355">
         <v>2</v>
       </c>
+      <c r="D355" t="s">
+        <v>578</v>
+      </c>
       <c r="E355" t="s">
         <v>62</v>
       </c>
@@ -7642,6 +9025,9 @@
       <c r="C356">
         <v>2</v>
       </c>
+      <c r="D356" t="s">
+        <v>579</v>
+      </c>
       <c r="E356" t="s">
         <v>62</v>
       </c>
@@ -7656,6 +9042,9 @@
       <c r="C357">
         <v>2</v>
       </c>
+      <c r="D357" t="s">
+        <v>580</v>
+      </c>
       <c r="E357" t="s">
         <v>62</v>
       </c>
@@ -7670,6 +9059,9 @@
       <c r="C358">
         <v>2</v>
       </c>
+      <c r="D358" t="s">
+        <v>581</v>
+      </c>
       <c r="E358" t="s">
         <v>62</v>
       </c>
@@ -7684,6 +9076,9 @@
       <c r="C359">
         <v>2</v>
       </c>
+      <c r="D359" t="s">
+        <v>582</v>
+      </c>
       <c r="E359" t="s">
         <v>62</v>
       </c>
@@ -7698,6 +9093,9 @@
       <c r="C360">
         <v>2</v>
       </c>
+      <c r="D360" t="s">
+        <v>583</v>
+      </c>
       <c r="E360" t="s">
         <v>62</v>
       </c>
@@ -7712,6 +9110,9 @@
       <c r="C361">
         <v>2</v>
       </c>
+      <c r="D361" t="s">
+        <v>584</v>
+      </c>
       <c r="E361" t="s">
         <v>62</v>
       </c>
@@ -7726,6 +9127,9 @@
       <c r="C362">
         <v>2</v>
       </c>
+      <c r="D362" t="s">
+        <v>585</v>
+      </c>
       <c r="E362" t="s">
         <v>62</v>
       </c>
@@ -7740,6 +9144,9 @@
       <c r="C363">
         <v>2</v>
       </c>
+      <c r="D363" t="s">
+        <v>586</v>
+      </c>
       <c r="E363" t="s">
         <v>62</v>
       </c>
@@ -7754,6 +9161,9 @@
       <c r="C364">
         <v>2</v>
       </c>
+      <c r="D364" t="s">
+        <v>587</v>
+      </c>
       <c r="E364" t="s">
         <v>62</v>
       </c>
@@ -7768,6 +9178,9 @@
       <c r="C365">
         <v>1</v>
       </c>
+      <c r="D365" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E365" t="s">
         <v>62</v>
       </c>
@@ -7782,6 +9195,9 @@
       <c r="C366">
         <v>1</v>
       </c>
+      <c r="D366" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E366" t="s">
         <v>307</v>
       </c>
@@ -7796,6 +9212,9 @@
       <c r="C367">
         <v>1</v>
       </c>
+      <c r="D367" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E367" t="s">
         <v>62</v>
       </c>
@@ -7810,6 +9229,9 @@
       <c r="C368">
         <v>2</v>
       </c>
+      <c r="D368" t="s">
+        <v>548</v>
+      </c>
       <c r="E368" t="s">
         <v>62</v>
       </c>
@@ -7824,6 +9246,9 @@
       <c r="C369">
         <v>2</v>
       </c>
+      <c r="D369" t="s">
+        <v>588</v>
+      </c>
       <c r="E369" t="s">
         <v>328</v>
       </c>
@@ -7838,6 +9263,9 @@
       <c r="C370">
         <v>1</v>
       </c>
+      <c r="D370" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E370" t="s">
         <v>330</v>
       </c>
@@ -7852,6 +9280,9 @@
       <c r="C371">
         <v>2</v>
       </c>
+      <c r="D371" t="s">
+        <v>585</v>
+      </c>
       <c r="E371" t="s">
         <v>331</v>
       </c>
@@ -7866,6 +9297,9 @@
       <c r="C372">
         <v>1</v>
       </c>
+      <c r="D372" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E372" t="s">
         <v>331</v>
       </c>
@@ -7880,6 +9314,9 @@
       <c r="C373">
         <v>2</v>
       </c>
+      <c r="D373" t="s">
+        <v>589</v>
+      </c>
       <c r="E373" t="s">
         <v>62</v>
       </c>
@@ -7894,6 +9331,9 @@
       <c r="C374">
         <v>1</v>
       </c>
+      <c r="D374" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E374" t="s">
         <v>334</v>
       </c>
@@ -7908,6 +9348,9 @@
       <c r="C375">
         <v>2</v>
       </c>
+      <c r="D375" t="s">
+        <v>590</v>
+      </c>
       <c r="E375" t="s">
         <v>62</v>
       </c>
@@ -7922,6 +9365,9 @@
       <c r="C376">
         <v>1</v>
       </c>
+      <c r="D376" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E376" t="s">
         <v>62</v>
       </c>
@@ -7936,6 +9382,9 @@
       <c r="C377">
         <v>2</v>
       </c>
+      <c r="D377" t="s">
+        <v>591</v>
+      </c>
       <c r="E377" t="s">
         <v>62</v>
       </c>
@@ -7950,6 +9399,9 @@
       <c r="C378">
         <v>2</v>
       </c>
+      <c r="D378" t="s">
+        <v>592</v>
+      </c>
       <c r="E378" t="s">
         <v>62</v>
       </c>
@@ -7964,6 +9416,9 @@
       <c r="C379">
         <v>2</v>
       </c>
+      <c r="D379" t="s">
+        <v>593</v>
+      </c>
       <c r="E379" t="s">
         <v>62</v>
       </c>
@@ -7978,6 +9433,9 @@
       <c r="C380">
         <v>2</v>
       </c>
+      <c r="D380" t="s">
+        <v>594</v>
+      </c>
       <c r="E380" t="s">
         <v>62</v>
       </c>
@@ -7992,6 +9450,9 @@
       <c r="C381">
         <v>2</v>
       </c>
+      <c r="D381" t="s">
+        <v>595</v>
+      </c>
       <c r="E381" t="s">
         <v>62</v>
       </c>
@@ -8006,6 +9467,9 @@
       <c r="C382">
         <v>1</v>
       </c>
+      <c r="D382" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E382" t="s">
         <v>62</v>
       </c>
@@ -8020,6 +9484,9 @@
       <c r="C383">
         <v>1</v>
       </c>
+      <c r="D383" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E383" t="s">
         <v>62</v>
       </c>
@@ -8034,6 +9501,9 @@
       <c r="C384">
         <v>2</v>
       </c>
+      <c r="D384" t="s">
+        <v>596</v>
+      </c>
       <c r="E384" t="s">
         <v>62</v>
       </c>
@@ -8048,6 +9518,9 @@
       <c r="C385">
         <v>2</v>
       </c>
+      <c r="D385" t="s">
+        <v>597</v>
+      </c>
       <c r="E385" t="s">
         <v>62</v>
       </c>
@@ -8062,6 +9535,9 @@
       <c r="C386">
         <v>2</v>
       </c>
+      <c r="D386" t="s">
+        <v>598</v>
+      </c>
       <c r="E386" t="s">
         <v>62</v>
       </c>
@@ -8076,6 +9552,12 @@
       <c r="C387">
         <v>3</v>
       </c>
+      <c r="D387" t="s">
+        <v>598</v>
+      </c>
+      <c r="E387" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
@@ -8087,6 +9569,9 @@
       <c r="C388">
         <v>2</v>
       </c>
+      <c r="D388" t="s">
+        <v>549</v>
+      </c>
       <c r="E388" t="s">
         <v>62</v>
       </c>
@@ -8101,6 +9586,9 @@
       <c r="C389">
         <v>2</v>
       </c>
+      <c r="D389" t="s">
+        <v>599</v>
+      </c>
       <c r="E389" t="s">
         <v>62</v>
       </c>
@@ -8115,6 +9603,9 @@
       <c r="C390">
         <v>2</v>
       </c>
+      <c r="D390" t="s">
+        <v>600</v>
+      </c>
       <c r="E390" t="s">
         <v>62</v>
       </c>
@@ -8129,6 +9620,9 @@
       <c r="C391">
         <v>2</v>
       </c>
+      <c r="D391" t="s">
+        <v>601</v>
+      </c>
       <c r="E391" t="s">
         <v>62</v>
       </c>
@@ -8143,6 +9637,9 @@
       <c r="C392">
         <v>2</v>
       </c>
+      <c r="D392" t="s">
+        <v>602</v>
+      </c>
       <c r="E392" t="s">
         <v>62</v>
       </c>
@@ -8157,6 +9654,9 @@
       <c r="C393">
         <v>1</v>
       </c>
+      <c r="D393" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E393" t="s">
         <v>62</v>
       </c>
@@ -8171,6 +9671,9 @@
       <c r="C394">
         <v>1</v>
       </c>
+      <c r="D394" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E394" t="s">
         <v>62</v>
       </c>
@@ -8185,6 +9688,9 @@
       <c r="C395">
         <v>2</v>
       </c>
+      <c r="D395" t="s">
+        <v>603</v>
+      </c>
       <c r="E395" t="s">
         <v>62</v>
       </c>
@@ -8199,6 +9705,9 @@
       <c r="C396">
         <v>2</v>
       </c>
+      <c r="D396" t="s">
+        <v>604</v>
+      </c>
       <c r="E396" t="s">
         <v>62</v>
       </c>
@@ -8213,6 +9722,9 @@
       <c r="C397">
         <v>2</v>
       </c>
+      <c r="D397" t="s">
+        <v>605</v>
+      </c>
       <c r="E397" t="s">
         <v>338</v>
       </c>
@@ -8227,6 +9739,9 @@
       <c r="C398">
         <v>2</v>
       </c>
+      <c r="D398" t="s">
+        <v>606</v>
+      </c>
       <c r="E398" t="s">
         <v>62</v>
       </c>
@@ -8241,6 +9756,9 @@
       <c r="C399">
         <v>3</v>
       </c>
+      <c r="D399" t="s">
+        <v>539</v>
+      </c>
       <c r="E399" t="s">
         <v>62</v>
       </c>
@@ -8255,6 +9773,9 @@
       <c r="C400">
         <v>1</v>
       </c>
+      <c r="D400" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E400" t="s">
         <v>307</v>
       </c>
@@ -8269,6 +9790,9 @@
       <c r="C401">
         <v>1</v>
       </c>
+      <c r="D401" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E401" t="s">
         <v>62</v>
       </c>
@@ -8283,6 +9807,9 @@
       <c r="C402">
         <v>2</v>
       </c>
+      <c r="D402" t="s">
+        <v>607</v>
+      </c>
       <c r="E402" t="s">
         <v>62</v>
       </c>
@@ -8297,6 +9824,9 @@
       <c r="C403">
         <v>2</v>
       </c>
+      <c r="D403" t="s">
+        <v>608</v>
+      </c>
       <c r="E403" t="s">
         <v>62</v>
       </c>
@@ -8311,6 +9841,9 @@
       <c r="C404">
         <v>2</v>
       </c>
+      <c r="D404" t="s">
+        <v>609</v>
+      </c>
       <c r="E404" t="s">
         <v>62</v>
       </c>
@@ -8325,6 +9858,9 @@
       <c r="C405">
         <v>2</v>
       </c>
+      <c r="D405" t="s">
+        <v>610</v>
+      </c>
       <c r="E405" t="s">
         <v>325</v>
       </c>
@@ -8339,6 +9875,9 @@
       <c r="C406">
         <v>3</v>
       </c>
+      <c r="D406" t="s">
+        <v>610</v>
+      </c>
       <c r="E406" t="s">
         <v>325</v>
       </c>
@@ -8353,6 +9892,9 @@
       <c r="C407">
         <v>2</v>
       </c>
+      <c r="D407" t="s">
+        <v>611</v>
+      </c>
       <c r="E407" t="s">
         <v>62</v>
       </c>
@@ -8367,6 +9909,9 @@
       <c r="C408">
         <v>2</v>
       </c>
+      <c r="D408" t="s">
+        <v>612</v>
+      </c>
       <c r="E408" t="s">
         <v>339</v>
       </c>
@@ -8381,6 +9926,9 @@
       <c r="C409">
         <v>3</v>
       </c>
+      <c r="D409" t="s">
+        <v>612</v>
+      </c>
       <c r="E409" t="s">
         <v>339</v>
       </c>
@@ -8395,6 +9943,9 @@
       <c r="C410">
         <v>2</v>
       </c>
+      <c r="D410" t="s">
+        <v>533</v>
+      </c>
       <c r="E410" t="s">
         <v>340</v>
       </c>
@@ -8409,6 +9960,9 @@
       <c r="C411">
         <v>2</v>
       </c>
+      <c r="D411" t="s">
+        <v>613</v>
+      </c>
       <c r="E411" t="s">
         <v>62</v>
       </c>
@@ -8423,6 +9977,9 @@
       <c r="C412">
         <v>2</v>
       </c>
+      <c r="D412" t="s">
+        <v>614</v>
+      </c>
       <c r="E412" t="s">
         <v>341</v>
       </c>
@@ -8437,6 +9994,9 @@
       <c r="C413">
         <v>2</v>
       </c>
+      <c r="D413" t="s">
+        <v>615</v>
+      </c>
       <c r="E413" t="s">
         <v>342</v>
       </c>
@@ -8451,6 +10011,12 @@
       <c r="C414">
         <v>3</v>
       </c>
+      <c r="D414" t="s">
+        <v>616</v>
+      </c>
+      <c r="E414" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
@@ -8462,6 +10028,9 @@
       <c r="C415">
         <v>1</v>
       </c>
+      <c r="D415" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E415" t="s">
         <v>62</v>
       </c>
@@ -8476,6 +10045,9 @@
       <c r="C416">
         <v>2</v>
       </c>
+      <c r="D416" t="s">
+        <v>617</v>
+      </c>
       <c r="E416" t="s">
         <v>62</v>
       </c>
@@ -8490,6 +10062,9 @@
       <c r="C417">
         <v>2</v>
       </c>
+      <c r="D417" t="s">
+        <v>618</v>
+      </c>
       <c r="E417" t="s">
         <v>62</v>
       </c>
@@ -8504,6 +10079,9 @@
       <c r="C418">
         <v>2</v>
       </c>
+      <c r="D418" t="s">
+        <v>619</v>
+      </c>
       <c r="E418" t="s">
         <v>62</v>
       </c>
@@ -8518,6 +10096,9 @@
       <c r="C419">
         <v>1</v>
       </c>
+      <c r="D419" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E419" t="s">
         <v>62</v>
       </c>
@@ -8532,6 +10113,9 @@
       <c r="C420">
         <v>2</v>
       </c>
+      <c r="D420" t="s">
+        <v>620</v>
+      </c>
       <c r="E420" t="s">
         <v>62</v>
       </c>
@@ -8546,6 +10130,9 @@
       <c r="C421">
         <v>2</v>
       </c>
+      <c r="D421" t="s">
+        <v>621</v>
+      </c>
       <c r="E421" t="s">
         <v>62</v>
       </c>
@@ -8560,6 +10147,9 @@
       <c r="C422">
         <v>1</v>
       </c>
+      <c r="D422" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="E422" t="s">
         <v>62</v>
       </c>
@@ -8573,6 +10163,9 @@
       </c>
       <c r="C423">
         <v>1</v>
+      </c>
+      <c r="D423" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="E423" t="s">
         <v>62</v>
@@ -8587,6 +10180,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -16090,6 +17687,9 @@
       <c r="A327" t="s">
         <v>61</v>
       </c>
+      <c r="B327" t="s">
+        <v>354</v>
+      </c>
       <c r="C327" t="s">
         <v>196</v>
       </c>
@@ -16616,6 +18216,9 @@
       <c r="A350" t="s">
         <v>66</v>
       </c>
+      <c r="B350" t="s">
+        <v>354</v>
+      </c>
       <c r="C350" t="s">
         <v>10</v>
       </c>
@@ -16820,6 +18423,9 @@
       <c r="A359" t="s">
         <v>66</v>
       </c>
+      <c r="B359" t="s">
+        <v>354</v>
+      </c>
       <c r="C359" t="s">
         <v>15</v>
       </c>
@@ -16840,6 +18446,9 @@
       <c r="A360" t="s">
         <v>66</v>
       </c>
+      <c r="B360" t="s">
+        <v>354</v>
+      </c>
       <c r="C360" t="s">
         <v>16</v>
       </c>
@@ -16860,6 +18469,9 @@
       <c r="A361" t="s">
         <v>66</v>
       </c>
+      <c r="B361" t="s">
+        <v>354</v>
+      </c>
       <c r="C361" t="s">
         <v>17</v>
       </c>
@@ -18121,6 +19733,9 @@
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>61</v>
+      </c>
+      <c r="B416" t="s">
+        <v>354</v>
       </c>
       <c r="C416" t="s">
         <v>47</v>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Escritorio\Python +POO\Clases Y objetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4F2451-8CA5-4AD9-9FCE-779620EF1369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7F751B-3254-41C9-8FC0-F385CA959C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6463" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="646">
   <si>
     <t>ID</t>
   </si>
@@ -1784,24 +1784,21 @@
     <t>EDANK</t>
   </si>
   <si>
-    <t>prueba</t>
-  </si>
-  <si>
-    <t>vaca</t>
-  </si>
-  <si>
-    <t>p+</t>
-  </si>
-  <si>
     <t>FECHA</t>
   </si>
   <si>
+    <t>CONFIRMACION PREÑEZ</t>
+  </si>
+  <si>
     <t>VELASQUEZ</t>
   </si>
   <si>
     <t>PARDO SUIZO</t>
   </si>
   <si>
+    <t>pendiente</t>
+  </si>
+  <si>
     <t>834/D9</t>
   </si>
   <si>
@@ -1913,9 +1910,6 @@
     <t>Hembra</t>
   </si>
   <si>
-    <t>hbr1523333</t>
-  </si>
-  <si>
     <t>116/5</t>
   </si>
   <si>
@@ -1968,9 +1962,6 @@
   </si>
   <si>
     <t xml:space="preserve"> hgy120387</t>
-  </si>
-  <si>
-    <t>pendiente</t>
   </si>
   <si>
     <t>Macho</t>
@@ -25802,39 +25793,8 @@
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>585</v>
-      </c>
-      <c r="B179" t="s">
-        <v>585</v>
-      </c>
-      <c r="C179" s="1">
-        <v>45870</v>
-      </c>
-      <c r="D179" s="1">
-        <v>45874</v>
-      </c>
-      <c r="E179" t="s">
-        <v>586</v>
-      </c>
-      <c r="F179" t="s">
-        <v>585</v>
-      </c>
-      <c r="G179" t="s">
-        <v>585</v>
-      </c>
-      <c r="H179" t="s">
-        <v>585</v>
-      </c>
-      <c r="I179" t="s">
-        <v>585</v>
-      </c>
-      <c r="J179" t="s">
-        <v>587</v>
-      </c>
-      <c r="K179" t="s">
-        <v>587</v>
-      </c>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25843,12 +25803,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -25859,8 +25823,11 @@
       <c r="D1" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46120</v>
       </c>
@@ -25868,13 +25835,16 @@
         <v>260</v>
       </c>
       <c r="C2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E2" t="s">
         <v>589</v>
       </c>
-      <c r="D2">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46120</v>
       </c>
@@ -25882,13 +25852,16 @@
         <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D3">
         <v>363</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46120</v>
       </c>
@@ -25899,10 +25872,13 @@
         <v>487</v>
       </c>
       <c r="D4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46120</v>
       </c>
@@ -25913,10 +25889,13 @@
         <v>487</v>
       </c>
       <c r="D5" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E5" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46120</v>
       </c>
@@ -25924,13 +25903,16 @@
         <v>298</v>
       </c>
       <c r="C6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D6">
         <v>328</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46120</v>
       </c>
@@ -25938,13 +25920,16 @@
         <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D7">
         <v>804</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46120</v>
       </c>
@@ -25952,13 +25937,16 @@
         <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D8">
         <v>804</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46120</v>
       </c>
@@ -25966,13 +25954,16 @@
         <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D9">
         <v>804</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46120</v>
       </c>
@@ -25980,27 +25971,33 @@
         <v>560</v>
       </c>
       <c r="C10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D10">
         <v>804</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46120</v>
       </c>
       <c r="B11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C11" t="s">
         <v>487</v>
       </c>
       <c r="D11" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E11" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46120</v>
       </c>
@@ -26008,27 +26005,33 @@
         <v>583</v>
       </c>
       <c r="C12" t="s">
+        <v>593</v>
+      </c>
+      <c r="D12" t="s">
         <v>594</v>
       </c>
-      <c r="D12" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46120</v>
       </c>
       <c r="B13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C13" t="s">
         <v>508</v>
       </c>
       <c r="D13" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+      <c r="E13" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46120</v>
       </c>
@@ -26039,32 +26042,41 @@
         <v>508</v>
       </c>
       <c r="D14" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+      <c r="E14" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46120</v>
       </c>
       <c r="B15" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+      <c r="E15" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46120</v>
       </c>
       <c r="B16" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C16" t="s">
         <v>508</v>
       </c>
       <c r="D16" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+      <c r="E16" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46120</v>
       </c>
@@ -26072,41 +26084,50 @@
         <v>500</v>
       </c>
       <c r="C17" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D17">
         <v>804</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46120</v>
       </c>
       <c r="B18" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C18" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D18">
         <v>219</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46120</v>
       </c>
       <c r="B19" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C19" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D19">
         <v>219</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46120</v>
       </c>
@@ -26117,10 +26138,13 @@
         <v>487</v>
       </c>
       <c r="D20" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E20" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46120</v>
       </c>
@@ -26131,10 +26155,13 @@
         <v>487</v>
       </c>
       <c r="D21" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46120</v>
       </c>
@@ -26142,27 +26169,33 @@
         <v>345</v>
       </c>
       <c r="C22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D22">
         <v>804</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46120</v>
       </c>
       <c r="B23" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C23" t="s">
         <v>487</v>
       </c>
       <c r="D23" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+      <c r="E23" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46120</v>
       </c>
@@ -26173,10 +26206,13 @@
         <v>487</v>
       </c>
       <c r="D24" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E24" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46120</v>
       </c>
@@ -26184,13 +26220,16 @@
         <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D25" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+      <c r="E25" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46120</v>
       </c>
@@ -26201,10 +26240,13 @@
         <v>487</v>
       </c>
       <c r="D26" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E26" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46120</v>
       </c>
@@ -26212,13 +26254,16 @@
         <v>356</v>
       </c>
       <c r="C27" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D27">
         <v>804</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46120</v>
       </c>
@@ -26226,13 +26271,16 @@
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D28">
         <v>804</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46120</v>
       </c>
@@ -26243,10 +26291,13 @@
         <v>487</v>
       </c>
       <c r="D29" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E29" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46120</v>
       </c>
@@ -26254,13 +26305,16 @@
         <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D30" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+      <c r="E30" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46120</v>
       </c>
@@ -26271,10 +26325,13 @@
         <v>487</v>
       </c>
       <c r="D31" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E31" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46120</v>
       </c>
@@ -26282,13 +26339,16 @@
         <v>349</v>
       </c>
       <c r="C32" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D32" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+      <c r="E32" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46120</v>
       </c>
@@ -26299,10 +26359,13 @@
         <v>487</v>
       </c>
       <c r="D33" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E33" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46120</v>
       </c>
@@ -26313,10 +26376,13 @@
         <v>487</v>
       </c>
       <c r="D34" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E34" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46121</v>
       </c>
@@ -26324,55 +26390,67 @@
         <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D35">
         <v>219</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46120</v>
       </c>
       <c r="B36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C36" t="s">
         <v>487</v>
       </c>
       <c r="D36" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E36" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46120</v>
       </c>
       <c r="B37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C37" t="s">
         <v>487</v>
       </c>
       <c r="D37" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E37" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46120</v>
       </c>
       <c r="B38" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C38" t="s">
         <v>487</v>
       </c>
       <c r="D38" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E38" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46120</v>
       </c>
@@ -26383,10 +26461,13 @@
         <v>487</v>
       </c>
       <c r="D39" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E39" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46120</v>
       </c>
@@ -26397,10 +26478,13 @@
         <v>487</v>
       </c>
       <c r="D40" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E40" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46120</v>
       </c>
@@ -26411,24 +26495,30 @@
         <v>487</v>
       </c>
       <c r="D41" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="E41" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46120</v>
       </c>
       <c r="B42" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C42" t="s">
         <v>487</v>
       </c>
       <c r="D42" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="E42" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46120</v>
       </c>
@@ -26439,10 +26529,13 @@
         <v>487</v>
       </c>
       <c r="D43" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E43" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46120</v>
       </c>
@@ -26450,13 +26543,16 @@
         <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D44">
         <v>804</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46120</v>
       </c>
@@ -26464,13 +26560,16 @@
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D45">
         <v>804</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46120</v>
       </c>
@@ -26481,10 +26580,13 @@
         <v>487</v>
       </c>
       <c r="D46" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="E46" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46120</v>
       </c>
@@ -26495,10 +26597,13 @@
         <v>487</v>
       </c>
       <c r="D47" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E47" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46120</v>
       </c>
@@ -26509,10 +26614,13 @@
         <v>487</v>
       </c>
       <c r="D48" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E48" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46120</v>
       </c>
@@ -26523,24 +26631,30 @@
         <v>487</v>
       </c>
       <c r="D49" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E49" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46120</v>
       </c>
       <c r="B50" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C50" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D50">
         <v>804</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46120</v>
       </c>
@@ -26548,13 +26662,16 @@
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D51">
         <v>804</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46120</v>
       </c>
@@ -26565,24 +26682,30 @@
         <v>487</v>
       </c>
       <c r="D52" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+      <c r="E52" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46120</v>
       </c>
       <c r="B53" t="s">
+        <v>612</v>
+      </c>
+      <c r="C53" t="s">
         <v>613</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>614</v>
       </c>
-      <c r="D53" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46120</v>
       </c>
@@ -26593,24 +26716,30 @@
         <v>487</v>
       </c>
       <c r="D54" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E54" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46120</v>
       </c>
       <c r="B55" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C55" t="s">
         <v>487</v>
       </c>
       <c r="D55" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E55" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46120</v>
       </c>
@@ -26621,10 +26750,13 @@
         <v>487</v>
       </c>
       <c r="D56" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+      <c r="E56" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46120</v>
       </c>
@@ -26635,10 +26767,13 @@
         <v>487</v>
       </c>
       <c r="D57" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E57" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46120</v>
       </c>
@@ -26649,10 +26784,13 @@
         <v>487</v>
       </c>
       <c r="D58" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E58" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46120</v>
       </c>
@@ -26660,13 +26798,16 @@
         <v>243</v>
       </c>
       <c r="C59" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D59">
         <v>378</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46120</v>
       </c>
@@ -26677,10 +26818,13 @@
         <v>487</v>
       </c>
       <c r="D60" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E60" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46120</v>
       </c>
@@ -26688,13 +26832,16 @@
         <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D61">
         <v>804</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -26705,10 +26852,13 @@
         <v>487</v>
       </c>
       <c r="D62" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E62" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -26719,10 +26869,13 @@
         <v>487</v>
       </c>
       <c r="D63" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+      <c r="E63" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46120</v>
       </c>
@@ -26733,10 +26886,13 @@
         <v>487</v>
       </c>
       <c r="D64" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E64" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46120</v>
       </c>
@@ -26747,10 +26903,13 @@
         <v>487</v>
       </c>
       <c r="D65" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E65" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46120</v>
       </c>
@@ -26761,10 +26920,13 @@
         <v>487</v>
       </c>
       <c r="D66" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="E66" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46120</v>
       </c>
@@ -26775,10 +26937,13 @@
         <v>487</v>
       </c>
       <c r="D67" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="E67" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46120</v>
       </c>
@@ -26789,24 +26954,30 @@
         <v>487</v>
       </c>
       <c r="D68" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="E68" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46120</v>
       </c>
       <c r="B69" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C69" t="s">
         <v>487</v>
       </c>
       <c r="D69" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+      <c r="E69" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46120</v>
       </c>
@@ -26817,10 +26988,13 @@
         <v>487</v>
       </c>
       <c r="D70" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="E70" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46120</v>
       </c>
@@ -26828,13 +27002,16 @@
         <v>120</v>
       </c>
       <c r="C71" t="s">
+        <v>617</v>
+      </c>
+      <c r="D71" t="s">
         <v>618</v>
       </c>
-      <c r="D71" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46120</v>
       </c>
@@ -26845,7 +27022,10 @@
         <v>487</v>
       </c>
       <c r="D72" t="s">
-        <v>608</v>
+        <v>607</v>
+      </c>
+      <c r="E72" t="s">
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -26875,7 +27055,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -26900,12 +27080,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -26920,12 +27100,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -26938,7 +27118,7 @@
   <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -26952,7 +27132,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E1" t="s">
         <v>479</v>
@@ -26972,19 +27152,19 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B2" t="s">
         <v>461</v>
       </c>
       <c r="C2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="F2" t="s">
         <v>485</v>
@@ -27001,16 +27181,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E3" t="s">
         <v>463</v>
@@ -27030,16 +27210,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B4" t="s">
         <v>465</v>
       </c>
       <c r="C4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E4" t="s">
         <v>464</v>
@@ -27059,16 +27239,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B5" t="s">
         <v>465</v>
       </c>
       <c r="C5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E5" t="s">
         <v>466</v>
@@ -27088,16 +27268,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B6" t="s">
         <v>465</v>
       </c>
       <c r="C6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E6" t="s">
         <v>464</v>
@@ -27117,16 +27297,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B7" t="s">
         <v>465</v>
       </c>
       <c r="C7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E7" t="s">
         <v>466</v>
@@ -27146,16 +27326,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B8" t="s">
         <v>465</v>
       </c>
       <c r="C8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E8" t="s">
         <v>464</v>
@@ -27175,16 +27355,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B9" t="s">
         <v>465</v>
       </c>
       <c r="C9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E9" t="s">
         <v>464</v>
@@ -27204,16 +27384,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B10" t="s">
         <v>465</v>
       </c>
       <c r="C10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D10" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E10" t="s">
         <v>464</v>
@@ -27233,16 +27413,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B11" t="s">
         <v>465</v>
       </c>
       <c r="C11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D11" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E11" t="s">
         <v>464</v>
@@ -27262,16 +27442,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B12" t="s">
         <v>461</v>
       </c>
       <c r="C12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D12" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E12" t="s">
         <v>467</v>
@@ -27291,16 +27471,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B13" t="s">
         <v>465</v>
       </c>
       <c r="C13" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D13" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E13" t="s">
         <v>468</v>
@@ -27320,16 +27500,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B14" t="s">
         <v>461</v>
       </c>
       <c r="C14" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D14" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E14" t="s">
         <v>469</v>
@@ -27349,16 +27529,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B15" t="s">
         <v>461</v>
       </c>
       <c r="C15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D15" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E15" t="s">
         <v>469</v>
@@ -27378,16 +27558,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B16" t="s">
         <v>461</v>
       </c>
       <c r="C16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D16" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E16" t="s">
         <v>470</v>
@@ -27407,16 +27587,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B17" t="s">
         <v>461</v>
       </c>
       <c r="C17" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D17" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E17" t="s">
         <v>469</v>
@@ -27436,16 +27616,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B18" t="s">
         <v>461</v>
       </c>
       <c r="C18" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D18" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E18" t="s">
         <v>469</v>
@@ -27465,16 +27645,16 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B19" t="s">
         <v>461</v>
       </c>
       <c r="C19" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D19" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E19" t="s">
         <v>469</v>
@@ -27494,16 +27674,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B20" t="s">
         <v>461</v>
       </c>
       <c r="C20" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D20" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E20" t="s">
         <v>469</v>
@@ -27523,16 +27703,16 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B21" t="s">
         <v>461</v>
       </c>
       <c r="C21" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D21" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E21" t="s">
         <v>470</v>
@@ -27552,16 +27732,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B22" t="s">
         <v>461</v>
       </c>
       <c r="C22" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D22" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E22" t="s">
         <v>469</v>
@@ -27581,16 +27761,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B23" t="s">
         <v>461</v>
       </c>
       <c r="C23" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D23" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E23" t="s">
         <v>470</v>
@@ -27610,16 +27790,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B24" t="s">
         <v>461</v>
       </c>
       <c r="C24" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D24" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E24" t="s">
         <v>471</v>
@@ -27639,16 +27819,16 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B25" t="s">
         <v>461</v>
       </c>
       <c r="C25" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D25" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E25" t="s">
         <v>470</v>
@@ -27668,16 +27848,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B26" t="s">
         <v>461</v>
       </c>
       <c r="C26" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D26" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E26" t="s">
         <v>470</v>
@@ -27697,16 +27877,16 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B27" t="s">
         <v>461</v>
       </c>
       <c r="C27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D27" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E27" t="s">
         <v>470</v>
@@ -27726,16 +27906,16 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D28" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E28" t="s">
         <v>473</v>
@@ -27755,16 +27935,16 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D29" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E29" t="s">
         <v>473</v>
@@ -27784,16 +27964,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D30" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E30" t="s">
         <v>473</v>
@@ -27813,16 +27993,16 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D31" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E31" t="s">
         <v>473</v>
@@ -27842,16 +28022,16 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D32" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E32" t="s">
         <v>473</v>
@@ -27871,16 +28051,16 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D33" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E33" t="s">
         <v>473</v>
@@ -27900,16 +28080,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D34" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E34" t="s">
         <v>473</v>
@@ -27929,16 +28109,16 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D35" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E35" t="s">
         <v>473</v>
@@ -27958,16 +28138,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D36" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E36" t="s">
         <v>473</v>
@@ -27987,16 +28167,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D37" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E37" t="s">
         <v>473</v>
@@ -28016,16 +28196,16 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D38" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E38" t="s">
         <v>473</v>
@@ -28045,16 +28225,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D39" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E39" t="s">
         <v>473</v>
@@ -28074,16 +28254,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D40" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E40" t="s">
         <v>473</v>
@@ -28103,16 +28283,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D41" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E41" t="s">
         <v>473</v>
@@ -28132,16 +28312,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D42" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E42" t="s">
         <v>473</v>
@@ -28161,16 +28341,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D43" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E43" t="s">
         <v>473</v>
@@ -28190,16 +28370,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D44" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E44" t="s">
         <v>473</v>
@@ -28219,16 +28399,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B45" t="s">
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D45" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E45" t="s">
         <v>473</v>
@@ -28248,16 +28428,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D46" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="E46" t="s">
         <v>473</v>
